--- a/hiring_companies_2026-10-29.xlsx
+++ b/hiring_companies_2026-10-29.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AO Globe Life</t>
+          <t>The Mice Groups, Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote Sales Representative</t>
+          <t>Senior User Interface Engineer</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8232411420229789787</t>
+          <t>https://jooble.org/jdp/1821684427704855541</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AO+Globe+Life</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Mice+Groups%2C+Inc.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HiredBuddy</t>
+          <t>Alpine Power Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>National UPS Sales Specialist</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-9099116604614540933</t>
+          <t>https://jooble.org/jdp/-874272980084488806</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=HiredBuddy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Alpine+Power+Systems</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Syndicate Labs</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lead Web Designer</t>
+          <t>Lead Full Stack Platform Engineer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1114587233660532157</t>
+          <t>https://jooble.org/jdp/-8909869602754818443</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Syndicate+Labs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=eBay</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hunter Bond</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Platform Engineer (HPC): $550,000 + Bonus/Benefits - Elite Fintech</t>
+          <t>Digital Platform Solutions Engineer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8760976943224639465</t>
+          <t>https://jooble.org/jdp/-3378807782193902227</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hunter+Bond</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bessemer+Trust</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,12 +665,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tekstraton</t>
+          <t>THORNDALE PARTNERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -680,22 +680,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Infrastructure Specialist | Data Platform Engineer (Databricks/Snowflake) | Senior Data Platform Engineer (Databricks / Snowflake) | Senior Full-Stack TypeScript &amp; Node Engineer | Senio</t>
+          <t>Regional Sales Manager</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4344864872526721798</t>
+          <t>https://jooble.org/jdp/2751133624709947997</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tekstraton</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=THORNDALE+PARTNERS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cypress HCM</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Remote Timeshare Sales Executive</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1434476984658848631</t>
+          <t>https://jooble.org/jdp/3515275133057304502</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cypress+HCM</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Smiles+Grins Ortho/Kids Dental</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Filtration Sales Specialist</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5133946076528673440</t>
+          <t>https://jooble.org/jdp/-6037712348150396420</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Smiles%2BGrins+Ortho%2FKids+Dental</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Danaher+Corporation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Royal Media</t>
+          <t>Karis Alliance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reporter</t>
+          <t>Regional Sales Manager - New Food</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7025665362345760472</t>
+          <t>https://jooble.org/jdp/1814121868076759308</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Royal+Media</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Karis+Alliance</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V-Soft Consulting Group, Inc.</t>
+          <t>Universal Health Care Lillington (AKA UHC/Lillington)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,22 +868,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Marketing Specialist III</t>
+          <t>Field Sales Rep</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/250135372303477100</t>
+          <t>https://jooble.org/jdp/1628687418058534433</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=V-Soft+Consulting+Group%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Universal+Health+Care+Lillington+%28AKA+UHC%2FLillington%29</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOROR By Satasha Stephen Beauty and Cosmetics</t>
+          <t>Hampa Studio</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Social Media Marketing Intern</t>
+          <t>2D ANIMATOR ARTISTS FOR VARIOUS PROJECTS (ALL LEVELS)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2343385670032837520</t>
+          <t>https://jooble.org/jdp/6867501452715200204</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SOROR+By+Satasha+Stephen+Beauty+and+Cosmetics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hampa+Studio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Olympus Cosmetic Group</t>
+          <t>Icreatives</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Healthcare Communications Writer 5W7WV36R | Videographer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8174122561537726773</t>
+          <t>https://jooble.org/jdp/-6677783201487509228</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Olympus+Cosmetic+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Icreatives</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NeuroScope Inc</t>
+          <t>M&amp;S Consulting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1009,22 +1009,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lead Software Engineer, Neuroimaging Platform</t>
+          <t>3D Animator | Java Developer (Mid-Level)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5030657063493522858</t>
+          <t>https://jooble.org/jdp/103721638329843699</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NeuroScope+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=M%26S+Consulting</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Climbing Steps</t>
+          <t>UpGuard Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Inside B2B Sales Representative - DME/HME Dealer Accounts (Uncapped Commission, Path to Sales Leadership)</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-633519164789573688</t>
+          <t>https://jooble.org/jdp/4476860953969088502</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Climbing+Steps</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=UpGuard+Inc.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Equiliem</t>
+          <t>Halstead Media</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sales Enablement Specialist</t>
+          <t>Senior Squarespace Website Designer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7439512432003964880</t>
+          <t>https://jooble.org/jdp/-625312680176695270</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Equiliem</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Halstead+Media</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Do You Convert</t>
+          <t>Variate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEM/PPC Specialist - Paid Search &amp; Paid Social</t>
+          <t>Senior UX Designer (UX/UI/Brand) (Remote, US-Based, Contractor)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8828851840930837098</t>
+          <t>https://jooble.org/jdp/-8316066849745304908</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Do+You+Convert</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Variate</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,12 +1182,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Anyone AI Inc.</t>
+          <t>Modus Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Marketing Expert</t>
+          <t>UX Designer - Contractor</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5411271252030463089</t>
+          <t>https://jooble.org/jdp/9163163947307844481</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Anyone+AI+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Modus+Digital</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,12 +1229,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Smoking Gun Interactive</t>
+          <t>ResMed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/697566290024237961</t>
+          <t>https://jooble.org/jdp/6630579259395224340</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Smoking+Gun+Interactive</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ResMed</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Life in Pittsburgh</t>
+          <t>Bravas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Home Experience Designer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4099780086184659821</t>
+          <t>https://jooble.org/jdp/8580323094317052377</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Life+in+Pittsburgh</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bravas</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Corps Team</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Inside Sales Representative- Medical Devices</t>
+          <t>On-Call Senior Lead Specialist, Issues Management and Media Relations</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7058215497614240924</t>
+          <t>https://jooble.org/jdp/-3129367354045642869</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Corps+Team</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ICF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,12 +1370,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>First American Home Warranty</t>
+          <t>Tonic3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Outbound Sales Specialist</t>
+          <t>Multimedia Copywriter</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8413583844826766264</t>
+          <t>https://jooble.org/jdp/8499087034728359782</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=First+American+Home+Warranty</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. Breuninger</t>
+          <t>Hidden Variable Studios LLC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Engineering Lead (m/w/d) Team Content // Remote möglich</t>
+          <t>Senior 3D Gameplay Animator</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3250494678193773570</t>
+          <t>https://jooble.org/jdp/7753658299427094768</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=E.+Breuninger</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hidden+Variable+Studios+LLC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Cube Care</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Senior Clinical System Designer</t>
+          <t>Marketing Director - Full Remote</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3795445026742181599</t>
+          <t>https://jooble.org/jdp/-3817315768318436664</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ICON+plc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Cube+Care</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shakti Solutions</t>
+          <t>Bernalillo County</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Linux exp</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4159662037719341522</t>
+          <t>https://jooble.org/jdp/-373064391331579345</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Shakti+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bernalillo+County</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20four7va</t>
+          <t>ICONMA, LLC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI &amp; ML Developer | Java Developer</t>
+          <t>Lead .NET Mobile Engineer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7442403187016420224</t>
+          <t>https://jooble.org/jdp/-8506577456474184183</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=20four7va</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ICONMA%2C+LLC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Blue Marble</t>
+          <t>ClickHouse</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>E-Commerce Marketing Specialist</t>
+          <t>Sr. Frontend Software Engineer - SysAdmin &amp; Internal Ops Platform</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/779008392316808477</t>
+          <t>https://jooble.org/jdp/9008678106491189724</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Blue+Marble</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ClickHouse</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ricavvo</t>
+          <t>Checkpoint Systems</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager</t>
+          <t>Senior Software Engineer- Embedded Linux Platform</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-874536290205964516</t>
+          <t>https://jooble.org/jdp/2443685482431929940</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ricavvo</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Checkpoint+Systems</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Smartsheet</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sr. Web UX Designer I (Remote Eligible - Costa Rica)</t>
+          <t>Principal Backend Engineer - Music Discovery Platform - Roon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7763146408735759473</t>
+          <t>https://jooble.org/jdp/6607468357611644116</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Smartsheet</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Harman</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,12 +1746,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Virtual Vocations Inc</t>
+          <t>CGH Group</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Video Editor | Experience Designer | Freelance Digital Graphic Designer | Freelance Video Editor | Senior Marketing Strategist | Senior UX Strategist | Senior Unity Engineer | UX Designer | </t>
+          <t>Remote Sales Specialist</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4825082293671417558</t>
+          <t>https://jooble.org/jdp/2213582434924679170</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Virtual+Vocations+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=CGH+Group</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scope Trade</t>
+          <t>Veracity Software Inc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>User Experience Designer</t>
+          <t>Senior Platform Engineer API</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7361748380587549694</t>
+          <t>https://jooble.org/jdp/-7639169978574881909</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Scope+Trade</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Veracity+Software+Inc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
+          <t>Agent Alliance Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1855,22 +1855,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Digital Media Producer at The Commonwealth Fund New York, NY</t>
+          <t>Remote Sales Representative</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2659961410355106462</t>
+          <t>https://jooble.org/jdp/-2432345609642927424</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Agent+Alliance+Inc.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Scale Army Careers</t>
+          <t>Premier Golf Sims</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Inside/Outside Sales Representative - Southern California</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7441832707547210413</t>
+          <t>https://jooble.org/jdp/-4968268652730259681</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Scale+Army+Careers</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Premier+Golf+Sims</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>RELEX Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Account Executive - Supply Chain SaaS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8131655593701729549</t>
+          <t>https://jooble.org/jdp/7404227201850555216</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=RELEX+Solutions</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Better Collective A/S</t>
+          <t>William &amp; Mary and the Virginia Institute of Marine Science</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Social Media Intern</t>
+          <t>Director, Media Relations</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3997354295208267017</t>
+          <t>https://jooble.org/jdp/-4019373497229737596</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Better+Collective+A%2FS</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=William+%26+Mary+and+the+Virginia+Institute+of+Marine+Science</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,12 +2028,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The SSI Group, LLC</t>
+          <t>Vivant Corporation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Senior Video Editor</t>
+          <t>Technical Sales Engineer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1875741981961423832</t>
+          <t>https://jooble.org/jdp/2214437897906277442</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+SSI+Group%2C+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Vivant+Corporation</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Easy HR Group</t>
+          <t>Intertek</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager | Video Editor</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8542786876637853314</t>
+          <t>https://jooble.org/jdp/-4420932141015262428</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Easy+HR+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Intertek</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Somewhere</t>
+          <t>Digital Nomad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Video Editor | Video Editor - Creative</t>
+          <t>Senior UX Designer</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2763956543653355839</t>
+          <t>https://jooble.org/jdp/7754855695041460088</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Somewhere</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Digital+Nomad</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Winsupply</t>
+          <t>Westinghouse Electric Company, LLC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Videographer</t>
+          <t>NucOps Procedure Writer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3037904779964500395</t>
+          <t>https://jooble.org/jdp/6180035850050586701</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Winsupply</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Westinghouse+Electric+Company%2C+LLC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,12 +2216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Teachers College, Columbia University</t>
+          <t>MVR Digital</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Higher Education Reporter</t>
+          <t>Senior Meta Ads Strategist and Media Buyer (Client-Facing)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1293984036131867729</t>
+          <t>https://jooble.org/jdp/-4072445965814362156</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Teachers+College%2C+Columbia+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MVR+Digital</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Well Connected Brands Inc.</t>
+          <t>Headlight</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paid Media Manager</t>
+          <t>Performance Marketing Specialist</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2148916567712854923</t>
+          <t>https://jooble.org/jdp/6052669987554961369</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Well+Connected+Brands+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Headlight</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Later</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator (US) | VP, Growth Marketing</t>
+          <t>Senior Software Engineer, Backend (AI Platform) | Senior Software Engineer, Backend (Reliability Platform)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1700525761871721992</t>
+          <t>https://jooble.org/jdp/2287152951777089876</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Later</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Affirm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Addison Group</t>
+          <t>ByLabs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Director of Performance Marketing</t>
+          <t>Principal Developer Platform Engineer - Financial Cloud</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-714573865275160356</t>
+          <t>https://jooble.org/jdp/4243321934842090750</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Addison+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ByLabs</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kelly Law Offices LLC</t>
+          <t>Sato Service Llc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Marketing Representative</t>
+          <t>Remote Sales Executive Uncapped Commission</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3312123608167357323</t>
+          <t>https://jooble.org/jdp/-8842546489388454657</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kelly+Law+Offices+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Sato+Service+Llc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASK Consulting LLC</t>
+          <t>ReminderMedia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Marketing Assistant</t>
+          <t>Sales Executive - Remote</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/299942635654528931</t>
+          <t>https://jooble.org/jdp/5752762560851377269</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ASK+Consulting+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ReminderMedia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Datacontroller Toogeza Ltd.</t>
+          <t>Beacon National Agency</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Marketing Director</t>
+          <t>Remote Sales Specialist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6138472496865073850</t>
+          <t>https://jooble.org/jdp/-2381404575386183796</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Datacontroller+Toogeza+Ltd.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Beacon+National+Agency</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Intelliswift</t>
+          <t>Millennia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>UI path developers - Remote</t>
+          <t>Vice President of Sales, Ambulatory</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-126742819810671072</t>
+          <t>https://jooble.org/jdp/5028050621994258550</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Intelliswift</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Millennia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tax Workout Group</t>
+          <t>SMB Team</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Senior Marketing Program Manager</t>
+          <t>Remote High-Ticket B2B Sales Executive Uncapped Commission</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6278272618813406257</t>
+          <t>https://jooble.org/jdp/-2029593415212228786</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tax+Workout+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SMB+Team</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ProCom</t>
+          <t>Steady Vision</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>212403 Mobile User Interface Developer</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1334442626926244119</t>
+          <t>https://jooble.org/jdp/-5373017049339422799</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ProCom</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Steady+Vision</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SRI Tech</t>
+          <t>Leading Edge Skills</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-723634464053876403</t>
+          <t>https://jooble.org/jdp/-5657397830266041173</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SRI+Tech</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Leading+Edge+Skills</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SA Technologies</t>
+          <t>Anchour</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ASP.net Front End Developer | Senior Software Engineer - Python / Linux/ Embedded &amp; IIoT</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4902616682363679191</t>
+          <t>https://jooble.org/jdp/-4495027270127323168</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SA+Technologies</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Anchour</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Engineering Director, Vercel for Platforms</t>
+          <t>Retail Store Manager</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3561157159801461169</t>
+          <t>https://jooble.org/jdp/-638087274713878922</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Vercel</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=PetSmart</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
